--- a/data/trans_orig/P6606-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6606-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2007</t>
+          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129135</t>
+          <t>127074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166641</t>
+          <t>166580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83100</t>
+          <t>82905</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107326</t>
+          <t>107409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218656</t>
+          <t>220505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>268089</t>
+          <t>265187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>99789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137027</t>
+          <t>136848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>37351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61627</t>
+          <t>61651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144051</t>
+          <t>143554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189207</t>
+          <t>188494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85884</t>
+          <t>84520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120770</t>
+          <t>120761</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93828</t>
+          <t>93983</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131062</t>
+          <t>131176</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>28401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>239555</t>
+          <t>240798</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>289594</t>
+          <t>291268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197341</t>
+          <t>197523</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>223937</t>
+          <t>223967</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443807</t>
+          <t>446917</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>505343</t>
+          <t>504007</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107404</t>
+          <t>107682</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148575</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>31283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54695</t>
+          <t>55097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144658</t>
+          <t>144804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193990</t>
+          <t>194350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105660</t>
+          <t>107362</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148787</t>
+          <t>147166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108526</t>
+          <t>110426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154422</t>
+          <t>155631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30312</t>
+          <t>29440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55513</t>
+          <t>55017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35838</t>
+          <t>37087</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64433</t>
+          <t>65908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176970</t>
+          <t>173818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218061</t>
+          <t>216599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160737</t>
+          <t>161159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183955</t>
+          <t>184185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345918</t>
+          <t>343867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>394253</t>
+          <t>393544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87011</t>
+          <t>86262</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121731</t>
+          <t>123767</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>40533</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111681</t>
+          <t>111811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154817</t>
+          <t>152999</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71627</t>
+          <t>70541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106687</t>
+          <t>106652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75701</t>
+          <t>77035</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112580</t>
+          <t>113703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32347</t>
+          <t>32488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>303047</t>
+          <t>299446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>349550</t>
+          <t>344689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>306323</t>
+          <t>305613</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>337061</t>
+          <t>335513</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>617048</t>
+          <t>621871</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>676022</t>
+          <t>677661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71309</t>
+          <t>70843</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103252</t>
+          <t>104943</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28426</t>
+          <t>29160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52931</t>
+          <t>53974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106171</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146824</t>
+          <t>148931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74057</t>
+          <t>76553</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>108685</t>
+          <t>111057</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29388</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>93796</t>
+          <t>90058</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131598</t>
+          <t>129979</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65169</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>43543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71862</t>
+          <t>73052</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>892735</t>
+          <t>891835</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>981429</t>
+          <t>981251</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>777593</t>
+          <t>777345</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828281</t>
+          <t>828077</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1683779</t>
+          <t>1681723</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1793542</t>
+          <t>1790728</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>396139</t>
+          <t>397426</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>470982</t>
+          <t>471526</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>137338</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>181921</t>
+          <t>184283</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>553946</t>
+          <t>549811</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>640151</t>
+          <t>637379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>372299</t>
+          <t>374603</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>447194</t>
+          <t>447681</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52320</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>407094</t>
+          <t>407587</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>486085</t>
+          <t>489249</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>105654</t>
+          <t>107978</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>150380</t>
+          <t>150960</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32079</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>124624</t>
+          <t>125507</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>172188</t>
+          <t>175001</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2012</t>
+          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59693</t>
+          <t>60030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88852</t>
+          <t>89185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60169</t>
+          <t>60686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86308</t>
+          <t>87327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126951</t>
+          <t>127462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169366</t>
+          <t>168058</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70967</t>
+          <t>70972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103453</t>
+          <t>101135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44817</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69096</t>
+          <t>68479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122778</t>
+          <t>123167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162864</t>
+          <t>163467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53668</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82580</t>
+          <t>82311</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73199</t>
+          <t>72453</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107514</t>
+          <t>105819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>29844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53672</t>
+          <t>54422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65945</t>
+          <t>64308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134731</t>
+          <t>132513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174219</t>
+          <t>171980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119949</t>
+          <t>119480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152993</t>
+          <t>152424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>262073</t>
+          <t>263442</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>316093</t>
+          <t>316428</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90660</t>
+          <t>91335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127785</t>
+          <t>127859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>73093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105210</t>
+          <t>104717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175020</t>
+          <t>173715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222098</t>
+          <t>222310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83015</t>
+          <t>83374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117054</t>
+          <t>118334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45016</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111563</t>
+          <t>110109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153788</t>
+          <t>153592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34370</t>
+          <t>35467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61410</t>
+          <t>60479</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>79568</t>
+          <t>78527</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89740</t>
+          <t>86633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124749</t>
+          <t>123514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104867</t>
+          <t>106513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136174</t>
+          <t>136116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203012</t>
+          <t>203170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253381</t>
+          <t>251111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84013</t>
+          <t>85650</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>123008</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>35313</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61483</t>
+          <t>61292</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>128069</t>
+          <t>129081</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>173064</t>
+          <t>175043</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60396</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93648</t>
+          <t>94391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>41623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>90459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128219</t>
+          <t>129020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47814</t>
+          <t>47519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34851</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62934</t>
+          <t>63579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>158646</t>
+          <t>160843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>198351</t>
+          <t>201201</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>164675</t>
+          <t>162339</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>199162</t>
+          <t>198111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>336201</t>
+          <t>333761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>391232</t>
+          <t>388989</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106660</t>
+          <t>106341</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>144053</t>
+          <t>145405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72350</t>
+          <t>72986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104079</t>
+          <t>103817</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>187703</t>
+          <t>188098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237443</t>
+          <t>237566</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>56218</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87127</t>
+          <t>86664</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30849</t>
+          <t>29949</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74511</t>
+          <t>74928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110057</t>
+          <t>110680</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30224</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56053</t>
+          <t>55702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>20146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>39926</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71539</t>
+          <t>69856</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>473689</t>
+          <t>474348</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>547035</t>
+          <t>549930</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>483059</t>
+          <t>481517</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>544384</t>
+          <t>547024</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>972948</t>
+          <t>975415</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1073004</t>
+          <t>1077484</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>386874</t>
+          <t>389936</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>461018</t>
+          <t>462171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>252297</t>
+          <t>252825</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>308350</t>
+          <t>310386</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>657948</t>
+          <t>660369</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>749159</t>
+          <t>753764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>280853</t>
+          <t>281715</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>346983</t>
+          <t>344816</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89745</t>
+          <t>87893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>128499</t>
+          <t>127998</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>384310</t>
+          <t>383871</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>458433</t>
+          <t>458744</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>140499</t>
+          <t>142571</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>189321</t>
+          <t>192032</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>35060</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>62885</t>
+          <t>61798</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>184824</t>
+          <t>183827</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>241809</t>
+          <t>238691</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2016</t>
+          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2016 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56737</t>
+          <t>56686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87209</t>
+          <t>86570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63614</t>
+          <t>64162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88004</t>
+          <t>88474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127770</t>
+          <t>128186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167876</t>
+          <t>166634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71040</t>
+          <t>71999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101277</t>
+          <t>100132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37035</t>
+          <t>37118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60662</t>
+          <t>58826</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115502</t>
+          <t>115845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154119</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45860</t>
+          <t>45267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71400</t>
+          <t>70904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40209</t>
+          <t>39979</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70082</t>
+          <t>71473</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104233</t>
+          <t>104561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>36553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23264</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28712</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53750</t>
+          <t>55066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>151333</t>
+          <t>150902</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193504</t>
+          <t>193794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128256</t>
+          <t>129984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>162070</t>
+          <t>165676</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>292599</t>
+          <t>291825</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>344568</t>
+          <t>343289</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101861</t>
+          <t>101778</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139074</t>
+          <t>138169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68618</t>
+          <t>66575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99187</t>
+          <t>97938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179985</t>
+          <t>179840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229428</t>
+          <t>227965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62709</t>
+          <t>63211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95661</t>
+          <t>95928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27410</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50647</t>
+          <t>51373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97157</t>
+          <t>99076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137018</t>
+          <t>138747</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48336</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>29826</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57901</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91701</t>
+          <t>94279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129679</t>
+          <t>130635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100956</t>
+          <t>102403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132669</t>
+          <t>132985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205231</t>
+          <t>205034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253468</t>
+          <t>251812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86191</t>
+          <t>85001</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122900</t>
+          <t>120911</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78310</t>
+          <t>77855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>109920</t>
+          <t>108942</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>172218</t>
+          <t>175795</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>220428</t>
+          <t>224578</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68821</t>
+          <t>67360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103684</t>
+          <t>101341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29018</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>51804</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104806</t>
+          <t>103664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145324</t>
+          <t>145223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48704</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80475</t>
+          <t>80353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30603</t>
+          <t>31066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68171</t>
+          <t>68013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104586</t>
+          <t>104655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190248</t>
+          <t>190935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>229872</t>
+          <t>231565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>209342</t>
+          <t>206513</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242624</t>
+          <t>240399</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>408338</t>
+          <t>409978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>464620</t>
+          <t>462120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70311</t>
+          <t>70945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102624</t>
+          <t>101556</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>42112</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66938</t>
+          <t>69457</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116686</t>
+          <t>118339</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159084</t>
+          <t>159017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>53380</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83128</t>
+          <t>82984</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>38348</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76977</t>
+          <t>76176</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>112970</t>
+          <t>113315</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46702</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28663</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68442</t>
+          <t>68582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>525580</t>
+          <t>529153</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>605321</t>
+          <t>600903</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>529539</t>
+          <t>533652</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>596920</t>
+          <t>595269</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1080479</t>
+          <t>1078960</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1182060</t>
+          <t>1179070</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>357535</t>
+          <t>361897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>429091</t>
+          <t>433060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>248523</t>
+          <t>249161</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>306215</t>
+          <t>305472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>627014</t>
+          <t>627337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>714450</t>
+          <t>721062</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>258270</t>
+          <t>257150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>321912</t>
+          <t>317813</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112321</t>
+          <t>113958</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155327</t>
+          <t>156101</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>382013</t>
+          <t>383948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>455800</t>
+          <t>457015</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>136173</t>
+          <t>135920</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>188050</t>
+          <t>187152</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>76692</t>
+          <t>76720</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>192995</t>
+          <t>195613</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>250221</t>
+          <t>253152</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2023</t>
+          <t>Población según la exposición a manipular cargas pesadas en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>29600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57883</t>
+          <t>58078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35279</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54183</t>
+          <t>54429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73134</t>
+          <t>70512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104473</t>
+          <t>104464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41493</t>
+          <t>42326</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71858</t>
+          <t>70798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52480</t>
+          <t>52874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82184</t>
+          <t>81052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115707</t>
+          <t>116125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34991</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54800</t>
+          <t>55613</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86003</t>
+          <t>85230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>17424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43453</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31229</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58068</t>
+          <t>61095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>199855</t>
+          <t>198239</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>481936</t>
+          <t>481082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75706</t>
+          <t>75432</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100944</t>
+          <t>100225</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>293084</t>
+          <t>290266</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>626275</t>
+          <t>611923</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23733</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155114</t>
+          <t>155229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56422</t>
+          <t>55911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80404</t>
+          <t>79896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56127</t>
+          <t>62108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229060</t>
+          <t>231093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132961</t>
+          <t>136280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20583</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37563</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152640</t>
+          <t>153993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69447</t>
+          <t>70365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>26218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84992</t>
+          <t>84274</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62795</t>
+          <t>63575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92456</t>
+          <t>92274</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42605</t>
+          <t>39362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100244</t>
+          <t>99148</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101712</t>
+          <t>104336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178743</t>
+          <t>177272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38572</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66455</t>
+          <t>66334</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>40072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>112074</t>
+          <t>114140</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>88417</t>
+          <t>90052</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>189495</t>
+          <t>183520</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>41975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28132</t>
+          <t>28812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58061</t>
+          <t>58060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116690</t>
+          <t>116194</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147724</t>
+          <t>147828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111061</t>
+          <t>112101</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>134364</t>
+          <t>134679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>235122</t>
+          <t>234448</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>273597</t>
+          <t>275207</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>24609</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49057</t>
+          <t>47599</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>28469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47371</t>
+          <t>47157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58979</t>
+          <t>57986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87826</t>
+          <t>87888</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25798</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49470</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41528</t>
+          <t>40706</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68840</t>
+          <t>68312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32599</t>
+          <t>32857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18622</t>
+          <t>18850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22916</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44564</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>457967</t>
+          <t>459929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>837608</t>
+          <t>820694</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>284370</t>
+          <t>271170</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>361670</t>
+          <t>360247</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>790040</t>
+          <t>790322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1225460</t>
+          <t>1265255</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118376</t>
+          <t>127887</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>296131</t>
+          <t>293546</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183779</t>
+          <t>183920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>296393</t>
+          <t>305646</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>283792</t>
+          <t>275497</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>528680</t>
+          <t>538166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94073</t>
+          <t>98676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>241693</t>
+          <t>244701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66103</t>
+          <t>65527</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98516</t>
+          <t>99650</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>174201</t>
+          <t>170088</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>318880</t>
+          <t>323320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>52008</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>136457</t>
+          <t>134316</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>63958</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>95106</t>
+          <t>95375</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>184836</t>
+          <t>185454</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6606-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6606-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127074</t>
+          <t>130569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166580</t>
+          <t>166611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82905</t>
+          <t>81458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107409</t>
+          <t>106447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>220505</t>
+          <t>220674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265187</t>
+          <t>267141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99789</t>
+          <t>101596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136848</t>
+          <t>137758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>61894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143554</t>
+          <t>145801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>188494</t>
+          <t>189349</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84520</t>
+          <t>85949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120761</t>
+          <t>120545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93983</t>
+          <t>91378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131176</t>
+          <t>129784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28401</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>240798</t>
+          <t>241837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>291268</t>
+          <t>290299</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197523</t>
+          <t>197626</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>223967</t>
+          <t>222769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>446917</t>
+          <t>448727</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>504007</t>
+          <t>504560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107682</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149700</t>
+          <t>147056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55097</t>
+          <t>54763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144804</t>
+          <t>144798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194350</t>
+          <t>192434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107362</t>
+          <t>105688</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147166</t>
+          <t>146213</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110426</t>
+          <t>109228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155631</t>
+          <t>154423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29440</t>
+          <t>29334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55017</t>
+          <t>55643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>35909</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>66127</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173818</t>
+          <t>175588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>216599</t>
+          <t>218337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161159</t>
+          <t>161580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184185</t>
+          <t>184293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343867</t>
+          <t>346098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393544</t>
+          <t>396440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,21%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86262</t>
+          <t>86606</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123767</t>
+          <t>123695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>20131</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40533</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111811</t>
+          <t>112919</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152999</t>
+          <t>155530</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70541</t>
+          <t>72245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106652</t>
+          <t>107495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77035</t>
+          <t>75337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113703</t>
+          <t>111080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27840</t>
+          <t>27449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>299446</t>
+          <t>303227</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>344689</t>
+          <t>349425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305613</t>
+          <t>306816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>335513</t>
+          <t>337858</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>621871</t>
+          <t>622750</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>677661</t>
+          <t>675619</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70843</t>
+          <t>70965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104943</t>
+          <t>106248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29160</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53974</t>
+          <t>52401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106059</t>
+          <t>105439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148931</t>
+          <t>145404</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76553</t>
+          <t>76061</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111057</t>
+          <t>111080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31116</t>
+          <t>30018</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>90058</t>
+          <t>92685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>129979</t>
+          <t>132021</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38264</t>
+          <t>38403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65588</t>
+          <t>65730</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43543</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73052</t>
+          <t>73231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>891835</t>
+          <t>890264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>981251</t>
+          <t>978190</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>777345</t>
+          <t>773445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828077</t>
+          <t>827451</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1681723</t>
+          <t>1681910</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1790728</t>
+          <t>1785751</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>397426</t>
+          <t>397864</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>471526</t>
+          <t>474167</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>137338</t>
+          <t>136324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184283</t>
+          <t>184846</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>549811</t>
+          <t>551003</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>637379</t>
+          <t>639072</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>374603</t>
+          <t>374678</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>447681</t>
+          <t>448317</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>53796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>407587</t>
+          <t>406247</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>489249</t>
+          <t>487717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107978</t>
+          <t>106054</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>150960</t>
+          <t>149857</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125507</t>
+          <t>124847</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>175001</t>
+          <t>172187</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>58538</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89185</t>
+          <t>88360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60686</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87327</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127462</t>
+          <t>127739</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168058</t>
+          <t>169266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70972</t>
+          <t>70987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101135</t>
+          <t>101951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41796</t>
+          <t>44400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68479</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123167</t>
+          <t>122631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163467</t>
+          <t>162653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52878</t>
+          <t>53607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82311</t>
+          <t>81525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72453</t>
+          <t>74218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105819</t>
+          <t>107821</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54422</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64308</t>
+          <t>65312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132513</t>
+          <t>132689</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>171980</t>
+          <t>174252</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119480</t>
+          <t>117883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152424</t>
+          <t>154037</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>263442</t>
+          <t>263267</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>316428</t>
+          <t>314197</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91335</t>
+          <t>91643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127859</t>
+          <t>127745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73093</t>
+          <t>72653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104717</t>
+          <t>106408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173715</t>
+          <t>173408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222310</t>
+          <t>224724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83374</t>
+          <t>80660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118334</t>
+          <t>117254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44100</t>
+          <t>45493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110109</t>
+          <t>110181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153592</t>
+          <t>151639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60479</t>
+          <t>61689</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46991</t>
+          <t>45567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78527</t>
+          <t>77772</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86633</t>
+          <t>87475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123514</t>
+          <t>126317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106513</t>
+          <t>105231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136116</t>
+          <t>136282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203170</t>
+          <t>201567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251111</t>
+          <t>252021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>86202</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123008</t>
+          <t>122618</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>61988</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>129081</t>
+          <t>127168</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175043</t>
+          <t>175272</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>62820</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94391</t>
+          <t>94258</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>43322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90459</t>
+          <t>91785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129020</t>
+          <t>128921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47519</t>
+          <t>48759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36225</t>
+          <t>34038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63579</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>160843</t>
+          <t>158006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>201201</t>
+          <t>200148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162339</t>
+          <t>162540</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198111</t>
+          <t>198491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>333761</t>
+          <t>333471</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>388989</t>
+          <t>386829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106341</t>
+          <t>106374</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145405</t>
+          <t>143837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72986</t>
+          <t>72730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103817</t>
+          <t>105003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188098</t>
+          <t>189375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237566</t>
+          <t>237339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56218</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86664</t>
+          <t>86923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29949</t>
+          <t>29756</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74928</t>
+          <t>74893</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110680</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>30131</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55702</t>
+          <t>56476</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20146</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69856</t>
+          <t>68947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>474348</t>
+          <t>475784</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>549930</t>
+          <t>554129</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>481517</t>
+          <t>479213</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>547024</t>
+          <t>545318</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>975415</t>
+          <t>974479</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1077484</t>
+          <t>1076928</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>389936</t>
+          <t>384545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>462171</t>
+          <t>459027</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>252825</t>
+          <t>252301</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>310386</t>
+          <t>312696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>660369</t>
+          <t>660055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>753764</t>
+          <t>751578</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>281715</t>
+          <t>280762</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>344816</t>
+          <t>345392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87893</t>
+          <t>87648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127998</t>
+          <t>127645</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>383871</t>
+          <t>381533</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>458744</t>
+          <t>456818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>142571</t>
+          <t>142322</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>192032</t>
+          <t>189696</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>34877</t>
+          <t>34785</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>61798</t>
+          <t>64917</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>183827</t>
+          <t>185398</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>238691</t>
+          <t>242974</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56686</t>
+          <t>59494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86570</t>
+          <t>87604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64162</t>
+          <t>62553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88474</t>
+          <t>87432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128186</t>
+          <t>126776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>166634</t>
+          <t>166283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71999</t>
+          <t>70752</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>101568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37118</t>
+          <t>37966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58826</t>
+          <t>58968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115845</t>
+          <t>117537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152959</t>
+          <t>154248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45267</t>
+          <t>45327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70904</t>
+          <t>70593</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39979</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71473</t>
+          <t>71206</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104561</t>
+          <t>103729</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>36473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29233</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55066</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150902</t>
+          <t>152160</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193794</t>
+          <t>193012</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129984</t>
+          <t>130925</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165676</t>
+          <t>163564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>291825</t>
+          <t>289557</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>343289</t>
+          <t>346409</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101778</t>
+          <t>102418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138169</t>
+          <t>138657</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66575</t>
+          <t>68146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97938</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179840</t>
+          <t>176443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>227965</t>
+          <t>227606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63211</t>
+          <t>62410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95928</t>
+          <t>93997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99076</t>
+          <t>97156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138747</t>
+          <t>135630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>47948</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55249</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>92442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130635</t>
+          <t>129234</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102403</t>
+          <t>101750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132985</t>
+          <t>133683</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205034</t>
+          <t>202725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251812</t>
+          <t>252595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85001</t>
+          <t>87019</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120911</t>
+          <t>121202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77855</t>
+          <t>78456</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>108942</t>
+          <t>108604</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>175795</t>
+          <t>174066</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>224578</t>
+          <t>221069</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67360</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101341</t>
+          <t>102877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51804</t>
+          <t>51554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103664</t>
+          <t>103205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145223</t>
+          <t>143478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>50062</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80353</t>
+          <t>80602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31066</t>
+          <t>30935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68013</t>
+          <t>68611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104655</t>
+          <t>105057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190935</t>
+          <t>189970</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>231565</t>
+          <t>233156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206513</t>
+          <t>207502</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>240399</t>
+          <t>241202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>409978</t>
+          <t>407132</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>462120</t>
+          <t>462316</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70945</t>
+          <t>68410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101556</t>
+          <t>101752</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42112</t>
+          <t>40849</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69457</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118339</t>
+          <t>118717</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159017</t>
+          <t>161419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53380</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82984</t>
+          <t>82646</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>39368</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76176</t>
+          <t>76501</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113315</t>
+          <t>113471</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24448</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47211</t>
+          <t>47452</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68582</t>
+          <t>69861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>529153</t>
+          <t>526315</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>600903</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>533652</t>
+          <t>531056</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>595269</t>
+          <t>595212</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1078960</t>
+          <t>1082155</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1179070</t>
+          <t>1179601</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>361897</t>
+          <t>357326</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>433060</t>
+          <t>430197</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>249161</t>
+          <t>251021</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>305472</t>
+          <t>306834</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>627337</t>
+          <t>629360</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>721062</t>
+          <t>715062</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>257150</t>
+          <t>257952</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>317813</t>
+          <t>319727</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>113546</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156101</t>
+          <t>157118</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>383948</t>
+          <t>383911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>457015</t>
+          <t>460737</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>135920</t>
+          <t>137518</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>187152</t>
+          <t>187080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>47694</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>76720</t>
+          <t>78823</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>195613</t>
+          <t>194431</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>253152</t>
+          <t>255881</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42902</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29600</t>
+          <t>36029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>65346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44112</t>
+          <t>47757</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>58718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>87014</t>
+          <t>96599</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70512</t>
+          <t>80201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104464</t>
+          <t>115977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>57357</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42326</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70798</t>
+          <t>72522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>47974</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52874</t>
+          <t>57277</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>97722</t>
+          <t>105332</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81052</t>
+          <t>89039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116125</t>
+          <t>123193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>54246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60588</t>
+          <t>68902</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>79463</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>64165</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85230</t>
+          <t>96882</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>33022</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t>50489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42610</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30932</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61095</t>
+          <t>67203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>358806</t>
+          <t>124668</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>198239</t>
+          <t>106113</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>481082</t>
+          <t>145609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88150</t>
+          <t>95487</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75432</t>
+          <t>81766</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100225</t>
+          <t>108631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>446957</t>
+          <t>220154</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>290266</t>
+          <t>197416</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>611923</t>
+          <t>247186</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80594</t>
+          <t>87894</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24346</t>
+          <t>70533</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155229</t>
+          <t>107283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>68014</t>
+          <t>74368</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55911</t>
+          <t>63071</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79896</t>
+          <t>88664</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>148609</t>
+          <t>162262</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62108</t>
+          <t>141862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231093</t>
+          <t>185132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69012</t>
+          <t>76923</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>60280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136280</t>
+          <t>94869</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>32132</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>42602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>97692</t>
+          <t>109054</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153993</t>
+          <t>130016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34190</t>
+          <t>43808</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70365</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>51970</t>
+          <t>62498</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>47557</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84274</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77576</t>
+          <t>82031</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63575</t>
+          <t>66025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92274</t>
+          <t>97711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75869</t>
+          <t>85989</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39362</t>
+          <t>74558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99148</t>
+          <t>97361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>153444</t>
+          <t>168020</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104336</t>
+          <t>148109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177272</t>
+          <t>188804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50675</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>47776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66334</t>
+          <t>81568</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68190</t>
+          <t>44088</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40072</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>114140</t>
+          <t>54900</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>118866</t>
+          <t>106345</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>87882</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>183520</t>
+          <t>126204</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>38450</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41975</t>
+          <t>52667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21972</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43505</t>
+          <t>54392</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28812</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58060</t>
+          <t>69796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32830</t>
+          <t>42715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>132409</t>
+          <t>144966</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116194</t>
+          <t>129525</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147828</t>
+          <t>161429</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>123896</t>
+          <t>136952</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112101</t>
+          <t>124954</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>134679</t>
+          <t>148695</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>256305</t>
+          <t>281918</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>234448</t>
+          <t>259485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>275207</t>
+          <t>302022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>34648</t>
+          <t>35163</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47599</t>
+          <t>47709</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36886</t>
+          <t>40883</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28469</t>
+          <t>31321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47157</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>71534</t>
+          <t>76046</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57986</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87888</t>
+          <t>95141</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>40951</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>30613</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>56214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>17755</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>53140</t>
+          <t>58705</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>46323</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68312</t>
+          <t>75186</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21932</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>17287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32857</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>21160</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>32861</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>28438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44482</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>611693</t>
+          <t>400507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>459929</t>
+          <t>368797</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>820694</t>
+          <t>435669</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>332027</t>
+          <t>366185</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>271170</t>
+          <t>342639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>360247</t>
+          <t>391698</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>943720</t>
+          <t>766692</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>790322</t>
+          <t>723996</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1265255</t>
+          <t>808894</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>220510</t>
+          <t>242671</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>127887</t>
+          <t>214158</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>293546</t>
+          <t>274238</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>216220</t>
+          <t>207314</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183920</t>
+          <t>186720</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>305646</t>
+          <t>229505</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>436731</t>
+          <t>449984</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>275497</t>
+          <t>417517</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>538166</t>
+          <t>485827</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>182327</t>
+          <t>210569</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98676</t>
+          <t>182224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>244701</t>
+          <t>238957</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>81190</t>
+          <t>91045</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65527</t>
+          <t>76338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99650</t>
+          <t>109255</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>263517</t>
+          <t>301615</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>170088</t>
+          <t>271116</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>323320</t>
+          <t>335546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>98466</t>
+          <t>124510</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>101209</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>134316</t>
+          <t>151642</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>55834</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>42202</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>63958</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>148973</t>
+          <t>180344</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>95375</t>
+          <t>152853</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>185454</t>
+          <t>211759</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
